--- a/r4-core-140-related-person/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
+++ b/r4-core-140-related-person/StructureDefinition-at-core-ext-address-municipalityCode.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Address Municipality Code</t>
+    <t>Address Municipality Code (Gemeindecode)</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-07T11:53:41+00:00</t>
+    <t>2026-10-15T12:52:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>HL7® Austria FHIR® Core Extension for the municipality code part of the Austrian address</t>
+    <t>HL7® Austria FHIR® Core Extension for the municipality code (Gemeindecode) part of the Austrian address. The municipality code is related to the [municipality key (Gemeindekennziffer)](StructureDefinition-at-core-ext-address-municipalityKey.html). While these two are generally identical, there is one notable exception: in Vienna, the municipality key (Gemeindekennziffer) is consistently 90001, whereas the municipality code (Gemeindecode) varies by district. The current list of values is provided by [Statistik Austria](https://www.statistik.at/verzeichnis/reglisten/gemliste_knz.pdf).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -135,7 +135,7 @@
     <t>element:Address</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address#Address</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address#Address</t>
   </si>
   <si>
     <t>ID</t>
